--- a/市场热度榜.xlsx
+++ b/市场热度榜.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liy22223\Desktop\FCN筛选器v1\screener\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liy22223\Desktop\FCN_老板候选池v8_转换\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94757240-854A-4544-88A7-21F6B4B2B991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B31F5FD-FFFC-4927-BFDC-288D8938747C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="77">
   <si>
     <t>区域</t>
   </si>
@@ -55,133 +55,145 @@
     <t>美股</t>
   </si>
   <si>
-    <t>AXTI US</t>
-  </si>
-  <si>
-    <t>AXT Inc</t>
+    <t>NBIS US</t>
+  </si>
+  <si>
+    <t>Nebius</t>
+  </si>
+  <si>
+    <t>AI基建</t>
+  </si>
+  <si>
+    <t>AI 云</t>
+  </si>
+  <si>
+    <t>欧式敲入</t>
+  </si>
+  <si>
+    <t>ALAB US</t>
+  </si>
+  <si>
+    <t>Astera Labs</t>
+  </si>
+  <si>
+    <t>AI 互联</t>
+  </si>
+  <si>
+    <t>MRVL US</t>
+  </si>
+  <si>
+    <t>Marvell</t>
+  </si>
+  <si>
+    <t>半导体</t>
+  </si>
+  <si>
+    <t>客制硅/互联</t>
+  </si>
+  <si>
+    <t>ARM US</t>
+  </si>
+  <si>
+    <t>Arm</t>
+  </si>
+  <si>
+    <t>AI 半导体 IP</t>
+  </si>
+  <si>
+    <t>GE US</t>
+  </si>
+  <si>
+    <t>GE 航空</t>
+  </si>
+  <si>
+    <t>工业</t>
+  </si>
+  <si>
+    <t>航空</t>
+  </si>
+  <si>
+    <t>CRDO US</t>
+  </si>
+  <si>
+    <t>Credo</t>
+  </si>
+  <si>
+    <t>HOOD US</t>
+  </si>
+  <si>
+    <t>Robinhood</t>
+  </si>
+  <si>
+    <t>金融</t>
+  </si>
+  <si>
+    <t>券商</t>
+  </si>
+  <si>
+    <t>FTNT US</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
   </si>
   <si>
     <t>科技</t>
   </si>
   <si>
-    <t>半导体设备与材料</t>
-  </si>
-  <si>
-    <t>欧式敲入</t>
-  </si>
-  <si>
-    <t>AAOI US</t>
-  </si>
-  <si>
-    <t>Applied Optoelectronics</t>
-  </si>
-  <si>
-    <t>通讯设备</t>
-  </si>
-  <si>
-    <t>SNDK US</t>
-  </si>
-  <si>
-    <t>闪迪</t>
-  </si>
-  <si>
-    <t>计算机硬件</t>
-  </si>
-  <si>
-    <t>NBIS US</t>
-  </si>
-  <si>
-    <t>NEBIUS</t>
-  </si>
-  <si>
-    <t>互联网内容与信息</t>
-  </si>
-  <si>
-    <t>BE US</t>
-  </si>
-  <si>
-    <t>Bloom Energy</t>
-  </si>
-  <si>
-    <t>电气设备及零件</t>
-  </si>
-  <si>
-    <t>IREN US</t>
-  </si>
-  <si>
-    <t>IREN Ltd</t>
-  </si>
-  <si>
-    <t>资本市场</t>
-  </si>
-  <si>
-    <t>CRDO US</t>
-  </si>
-  <si>
-    <t>Credo Technology</t>
-  </si>
-  <si>
-    <t>半导体</t>
-  </si>
-  <si>
-    <t>INTC US</t>
-  </si>
-  <si>
-    <t>英特尔</t>
-  </si>
-  <si>
-    <t>ASTS US</t>
-  </si>
-  <si>
-    <t>AST SpaceMobile</t>
-  </si>
-  <si>
-    <t>IONQ US</t>
-  </si>
-  <si>
-    <t>IonQ Inc</t>
-  </si>
-  <si>
-    <t>CBRS US</t>
-  </si>
-  <si>
-    <t>Cerebras Systems</t>
-  </si>
-  <si>
-    <t>MRVL US</t>
-  </si>
-  <si>
-    <t>迈威尔科技</t>
-  </si>
-  <si>
-    <t>ALAB US</t>
-  </si>
-  <si>
-    <t>Astera Labs</t>
+    <t>网络安全</t>
+  </si>
+  <si>
+    <t>MU US</t>
+  </si>
+  <si>
+    <t>美光</t>
+  </si>
+  <si>
+    <t>内存/HBM</t>
+  </si>
+  <si>
+    <t>AMD US</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>AI 芯片</t>
+  </si>
+  <si>
+    <t>AMAT US</t>
+  </si>
+  <si>
+    <t>应用材料</t>
+  </si>
+  <si>
+    <t>半导体设备</t>
+  </si>
+  <si>
+    <t>LRCX US</t>
+  </si>
+  <si>
+    <t>泛林集团</t>
+  </si>
+  <si>
+    <t>DELL US</t>
+  </si>
+  <si>
+    <t>戴尔</t>
+  </si>
+  <si>
+    <t>AI 服务器</t>
   </si>
   <si>
     <t>港股</t>
   </si>
   <si>
-    <t>2513 HK</t>
-  </si>
-  <si>
-    <t>智谱</t>
-  </si>
-  <si>
-    <t>数码解决方案服务</t>
-  </si>
-  <si>
-    <t>100 HK</t>
-  </si>
-  <si>
-    <t>MINIMAX-W</t>
-  </si>
-  <si>
-    <t>9903 HK</t>
-  </si>
-  <si>
-    <t>天数智芯</t>
+    <t>1347 HK</t>
+  </si>
+  <si>
+    <t>华虹半导体</t>
+  </si>
+  <si>
+    <t>晶圆代工</t>
   </si>
   <si>
     <t>6869 HK</t>
@@ -190,28 +202,55 @@
     <t>长飞光纤光缆</t>
   </si>
   <si>
-    <t>电讯网路基建设施</t>
-  </si>
-  <si>
-    <t>6166 HK</t>
-  </si>
-  <si>
-    <t>剑桥科技</t>
-  </si>
-  <si>
-    <t>2476 HK</t>
-  </si>
-  <si>
-    <t>胜宏科技</t>
-  </si>
-  <si>
-    <t>电子零件</t>
-  </si>
-  <si>
-    <t>2631 HK</t>
-  </si>
-  <si>
-    <t>天岳先进</t>
+    <t>AI硬件</t>
+  </si>
+  <si>
+    <t>AI 光通信</t>
+  </si>
+  <si>
+    <t>992 HK</t>
+  </si>
+  <si>
+    <t>联想</t>
+  </si>
+  <si>
+    <t>AI/PC</t>
+  </si>
+  <si>
+    <t>2359 HK</t>
+  </si>
+  <si>
+    <t>药明康德</t>
+  </si>
+  <si>
+    <t>医疗</t>
+  </si>
+  <si>
+    <t>CDMO</t>
+  </si>
+  <si>
+    <t>981 HK</t>
+  </si>
+  <si>
+    <t>中芯国际</t>
+  </si>
+  <si>
+    <t>522 HK</t>
+  </si>
+  <si>
+    <t>ASMPT</t>
+  </si>
+  <si>
+    <t>9992 HK</t>
+  </si>
+  <si>
+    <t>泡泡玛特</t>
+  </si>
+  <si>
+    <t>消费</t>
+  </si>
+  <si>
+    <t>潮玩 IP</t>
   </si>
 </sst>
 </file>
@@ -584,7 +623,7 @@
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="7" width="8" customWidth="1"/>
@@ -653,7 +692,7 @@
         <v>1.01</v>
       </c>
       <c r="J2" s="3">
-        <v>0.53810000000000002</v>
+        <v>0.58530000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -667,7 +706,7 @@
         <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -685,7 +724,7 @@
         <v>1.01</v>
       </c>
       <c r="J3" s="3">
-        <v>0.58289999999999997</v>
+        <v>0.52549999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -699,10 +738,10 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2">
         <v>0.8</v>
@@ -717,7 +756,7 @@
         <v>1.01</v>
       </c>
       <c r="J4" s="3">
-        <v>0.5585</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -725,16 +764,16 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2">
         <v>0.8</v>
@@ -749,7 +788,7 @@
         <v>1.01</v>
       </c>
       <c r="J5" s="3">
-        <v>0.58650000000000002</v>
+        <v>0.46550000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -757,16 +796,16 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F6" s="2">
         <v>0.8</v>
@@ -781,7 +820,7 @@
         <v>1.01</v>
       </c>
       <c r="J6" s="3">
-        <v>0.55900000000000005</v>
+        <v>7.6799999999999993E-2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -789,16 +828,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F7" s="2">
         <v>0.8</v>
@@ -813,7 +852,7 @@
         <v>1.01</v>
       </c>
       <c r="J7" s="3">
-        <v>0.48249999999999998</v>
+        <v>0.4899</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -821,16 +860,16 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F8" s="2">
         <v>0.8</v>
@@ -845,7 +884,7 @@
         <v>1.01</v>
       </c>
       <c r="J8" s="3">
-        <v>0.50880000000000003</v>
+        <v>0.29499999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -853,16 +892,16 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F9" s="2">
         <v>0.8</v>
@@ -877,7 +916,7 @@
         <v>1.01</v>
       </c>
       <c r="J9" s="3">
-        <v>0.41420000000000001</v>
+        <v>0.1779</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -885,16 +924,16 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2">
         <v>0.8</v>
@@ -909,7 +948,7 @@
         <v>1.01</v>
       </c>
       <c r="J10" s="3">
-        <v>0.49540000000000001</v>
+        <v>0.39219999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -917,16 +956,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F11" s="2">
         <v>0.8</v>
@@ -941,7 +980,7 @@
         <v>1.01</v>
       </c>
       <c r="J11" s="3">
-        <v>0.44519999999999998</v>
+        <v>0.31759999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -949,16 +988,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F12" s="2">
         <v>0.8</v>
@@ -973,7 +1012,7 @@
         <v>1.01</v>
       </c>
       <c r="J12" s="3">
-        <v>0.2016</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -981,16 +1020,16 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F13" s="2">
         <v>0.8</v>
@@ -1005,7 +1044,7 @@
         <v>1.01</v>
       </c>
       <c r="J13" s="3">
-        <v>0.45760000000000001</v>
+        <v>0.34670000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1013,16 +1052,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F14" s="2">
         <v>0.8</v>
@@ -1037,24 +1076,24 @@
         <v>1.01</v>
       </c>
       <c r="J14" s="3">
-        <v>0.52459999999999996</v>
+        <v>0.3624</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2">
         <v>0.8</v>
@@ -1069,24 +1108,24 @@
         <v>1.01</v>
       </c>
       <c r="J15" s="3">
-        <v>0.42899999999999999</v>
+        <v>0.37140000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F16" s="2">
         <v>0.8</v>
@@ -1101,24 +1140,24 @@
         <v>1.01</v>
       </c>
       <c r="J16" s="3">
-        <v>0.56110000000000004</v>
+        <v>0.5363</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F17" s="2">
         <v>0.8</v>
@@ -1133,24 +1172,24 @@
         <v>1.01</v>
       </c>
       <c r="J17" s="3">
-        <v>0.19800000000000001</v>
+        <v>0.1905</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C18" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="F18" s="2">
         <v>0.8</v>
@@ -1165,25 +1204,25 @@
         <v>1.01</v>
       </c>
       <c r="J18" s="3">
-        <v>0.54059999999999997</v>
+        <v>0.1227</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
         <v>57</v>
       </c>
-      <c r="C19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>56</v>
-      </c>
       <c r="F19" s="2">
         <v>0.8</v>
       </c>
@@ -1197,24 +1236,24 @@
         <v>1.01</v>
       </c>
       <c r="J19" s="3">
-        <v>0.19819999999999999</v>
+        <v>0.24199999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F20" s="2">
         <v>0.8</v>
@@ -1229,24 +1268,24 @@
         <v>1.01</v>
       </c>
       <c r="J20" s="3">
-        <v>0.308</v>
+        <v>0.23200000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="F21" s="2">
         <v>0.8</v>
@@ -1261,7 +1300,7 @@
         <v>1.01</v>
       </c>
       <c r="J21" s="3">
-        <v>0.27029999999999998</v>
+        <v>0.15010000000000001</v>
       </c>
     </row>
   </sheetData>
